--- a/hanbit_mvp_dataset_phase1/24_gl_transaction.xlsx
+++ b/hanbit_mvp_dataset_phase1/24_gl_transaction.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gl_transaction" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="gl_transaction" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'gl_transaction'!$A$1:$I$45</definedName>
@@ -550,7 +550,6 @@
       <c r="H3" t="n">
         <v>120000</v>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -628,7 +627,6 @@
       <c r="H5" t="n">
         <v>180000</v>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -706,7 +704,6 @@
       <c r="H7" t="n">
         <v>60000</v>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -784,7 +781,6 @@
       <c r="H9" t="n">
         <v>90000</v>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -862,7 +858,6 @@
       <c r="H11" t="n">
         <v>80000</v>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -940,7 +935,6 @@
       <c r="H13" t="n">
         <v>60000</v>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1018,7 +1012,6 @@
       <c r="H15" t="n">
         <v>45000</v>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1096,7 +1089,6 @@
       <c r="H17" t="n">
         <v>30000</v>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1133,7 +1125,6 @@
       <c r="H18" t="n">
         <v>0</v>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1170,7 +1161,6 @@
       <c r="H19" t="n">
         <v>25000</v>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1207,7 +1197,6 @@
       <c r="H20" t="n">
         <v>0</v>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1244,7 +1233,6 @@
       <c r="H21" t="n">
         <v>80000</v>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1322,7 +1310,6 @@
       <c r="H23" t="n">
         <v>10000</v>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1400,7 +1387,6 @@
       <c r="H25" t="n">
         <v>10000</v>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1478,7 +1464,6 @@
       <c r="H27" t="n">
         <v>10000</v>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1556,7 +1541,6 @@
       <c r="H29" t="n">
         <v>10000</v>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1634,7 +1618,6 @@
       <c r="H31" t="n">
         <v>10000</v>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1712,7 +1695,6 @@
       <c r="H33" t="n">
         <v>10000</v>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1790,7 +1772,6 @@
       <c r="H35" t="n">
         <v>10000</v>
       </c>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1868,7 +1849,6 @@
       <c r="H37" t="n">
         <v>10000</v>
       </c>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1946,7 +1926,6 @@
       <c r="H39" t="n">
         <v>10000</v>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2024,7 +2003,6 @@
       <c r="H41" t="n">
         <v>10000</v>
       </c>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2088,7 +2066,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2102,7 +2080,6 @@
       <c r="H43" t="n">
         <v>10000</v>
       </c>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2180,7 +2157,6 @@
       <c r="H45" t="n">
         <v>10000</v>
       </c>
-      <c r="I45" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I45"/>
